--- a/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海嵎 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1305,7 +1169,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1351,7 +1215,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1397,7 +1261,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1443,7 +1307,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1489,7 +1353,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1535,7 +1399,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1581,7 +1445,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1627,7 +1491,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1673,7 +1537,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1719,7 +1583,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1765,7 +1629,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2157,7 +2021,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2203,7 +2067,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2249,7 +2113,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2295,7 +2159,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2341,7 +2205,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2387,7 +2251,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2433,7 +2297,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2479,7 +2343,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2525,7 +2389,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2571,7 +2435,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2617,7 +2481,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2663,7 +2527,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2709,7 +2573,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2755,7 +2619,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2801,7 +2665,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2847,7 +2711,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2893,7 +2757,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2939,7 +2803,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2985,7 +2849,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3031,7 +2895,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3077,7 +2941,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3123,7 +2987,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3169,7 +3033,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3261,7 +3125,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3307,7 +3171,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3353,7 +3217,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3399,7 +3263,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3445,7 +3309,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3491,7 +3355,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3537,7 +3401,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3583,7 +3447,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3629,7 +3493,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3675,7 +3539,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3721,7 +3585,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3767,7 +3631,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3813,7 +3677,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3859,7 +3723,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3905,7 +3769,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3951,7 +3815,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3997,7 +3861,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4043,7 +3907,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4089,7 +3953,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4135,7 +3999,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4181,7 +4045,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4227,7 +4091,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4273,7 +4137,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4319,7 +4183,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4365,7 +4229,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4411,7 +4275,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4457,7 +4321,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4503,7 +4367,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4549,7 +4413,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4595,7 +4459,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4641,7 +4505,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4687,7 +4551,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4733,7 +4597,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4779,7 +4643,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4825,7 +4689,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4871,7 +4735,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4917,7 +4781,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4963,7 +4827,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5009,7 +4873,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5055,7 +4919,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5101,7 +4965,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5147,7 +5011,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5193,7 +5057,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5239,7 +5103,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5285,7 +5149,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5331,7 +5195,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5377,7 +5241,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5423,7 +5287,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5469,7 +5333,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5515,7 +5379,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5561,7 +5425,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5607,7 +5471,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5653,7 +5517,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5699,7 +5563,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5745,7 +5609,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5791,7 +5655,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5837,7 +5701,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5883,7 +5747,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5929,7 +5793,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5975,7 +5839,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6021,7 +5885,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6067,7 +5931,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6113,7 +5977,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6159,7 +6023,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6205,7 +6069,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6301,7 +6165,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6347,7 +6211,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6393,7 +6257,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6439,7 +6303,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6511,1300 +6375,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海嵎 - 海嵎 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>125 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>105 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1063呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 471呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 471呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$1,016万
-$35,401/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$1,026万
-$36,144/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$1,028万
-$36,215/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$1,153万
-$35,477/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,425万
-$34,587/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$994万
-$34,627/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$1,011万
-$35,595/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$1,013万
-$35,665/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$1,139万
-$35,040/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,410万
-$34,223/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$993万
-$34,479/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$953万
-$33,206/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$977万
-$34,398/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$980万
-$34,507/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$1,110万
-$34,154/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,376万
-$33,400/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$915万
-$31,771/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$924万
-$32,181/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$946万
-$33,327/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$948万
-$33,373/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$1,076万
-$33,108/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,333万
-$32,354/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$896万
-$31,111/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$916万
-$31,923/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$937万
-$33,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$940万
-$33,081/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$1,078万
-$33,169/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,322万
-$32,095/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$898万
-$31,181/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$903万
-$31,470/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$927万
-$32,637/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$929万
-$32,701/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$1,056万
-$32,477/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,307万
-$31,728/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$868万
-$30,139/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$898万
-$31,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$918万
-$32,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$920万
-$32,377/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$1,045万
-$32,154/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,294万
-$31,415/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$860万
-$29,858/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$868万
-$30,244/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$888万
-$31,268/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$891万
-$31,359/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$1,023万
-$31,477/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,253万
-$30,408/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$834万
-$28,951/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$812万
-$28,310/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$832万
-$29,296/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$834万
-$29,352/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$947万
-$29,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,173万
-$28,464/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$780万
-$27,101/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$804万
-$28,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$823万
-$28,972/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$824万
-$29,028/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$936万
-$28,806/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,160万
-$28,148/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$772万
-$26,802/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$821万
-$28,596/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$843万
-$29,683/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$845万
-$29,754/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$956万
-$29,422/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,184万
-$28,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$788万
-$27,375/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$786万
-$27,401/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$805万
-$28,352/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$807万
-$28,408/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$916万
-$28,191/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,135万
-$27,546/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$755万
-$26,229/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$778万
-$27,115/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$797万
-$28,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$798万
-$28,113/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$907万
-$27,898/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,123万
-$27,262/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$748万
-$25,958/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$769万
-$26,805/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$788万
-$27,732/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$789万
-$27,792/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$896万
-$27,578/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,110万
-$26,947/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$739万
-$25,656/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$761万
-$26,519/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$779万
-$27,440/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$781万
-$27,496/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$887万
-$27,283/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,098万
-$26,660/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$731万
-$25,385/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$752万
-$26,206/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$770万
-$27,116/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$772万
-$27,169/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$876万
-$26,963/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,085万
-$26,345/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$722万
-$25,087/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 287呎 (1房)
-$744万
-$25,920/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
-$762万
-$26,820/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$763万
-$26,873/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$867万
-$26,668/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
-$1,074万
-$26,061/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 288呎 (1房)
-$715万
-$24,812/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 247呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$753万
-$26,339/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$755万
-$26,581/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 325呎 (1房)
-$857万
-$26,375/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 374呎 (2房)
-$1,350万
-$36,096/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G27" s="19" t="inlineStr">
-        <is>
-          <t>F | 251呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海嵎" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -6375,4 +6554,1300 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>海嵎 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1063呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 471呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 471呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$1016万
+$35,401/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$1026万
+$36,144/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$1028万
+$36,215/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$1153万
+$35,477/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1425万
+$34,587/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$994万
+$34,627/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$1011万
+$35,595/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$1013万
+$35,665/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$1139万
+$35,040/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1410万
+$34,223/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$993万
+$34,479/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$953万
+$33,206/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$977万
+$34,398/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$980万
+$34,507/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$1110万
+$34,154/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1376万
+$33,400/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$915万
+$31,771/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$924万
+$32,181/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$946万
+$33,327/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$948万
+$33,373/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$1076万
+$33,108/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1333万
+$32,354/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$896万
+$31,111/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$916万
+$31,923/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$937万
+$33,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$940万
+$33,081/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$1078万
+$33,169/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1322万
+$32,095/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$898万
+$31,181/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$903万
+$31,470/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$927万
+$32,637/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$929万
+$32,701/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$1056万
+$32,477/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1307万
+$31,728/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$868万
+$30,139/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$898万
+$31,300/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$918万
+$32,324/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$920万
+$32,377/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$1045万
+$32,154/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1294万
+$31,415/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$860万
+$29,858/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$868万
+$30,244/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$888万
+$31,268/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$891万
+$31,359/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$1023万
+$31,477/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1253万
+$30,408/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$834万
+$28,951/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$812万
+$28,310/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$832万
+$29,296/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$834万
+$29,352/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$947万
+$29,129/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1173万
+$28,464/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$780万
+$27,101/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$804万
+$28,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$823万
+$28,972/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$824万
+$29,028/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$936万
+$28,806/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1160万
+$28,148/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$772万
+$26,802/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$821万
+$28,596/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$843万
+$29,683/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$845万
+$29,754/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$956万
+$29,422/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1184万
+$28,750/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$788万
+$27,375/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$786万
+$27,401/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$805万
+$28,352/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$807万
+$28,408/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$916万
+$28,191/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1135万
+$27,546/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$755万
+$26,229/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$778万
+$27,115/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$797万
+$28,060/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$798万
+$28,113/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$907万
+$27,898/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1123万
+$27,262/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$748万
+$25,958/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$769万
+$26,805/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$788万
+$27,732/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$789万
+$27,792/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$896万
+$27,578/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1110万
+$26,947/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$739万
+$25,656/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$761万
+$26,519/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$779万
+$27,440/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$781万
+$27,496/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$887万
+$27,283/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1098万
+$26,660/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$731万
+$25,385/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$752万
+$26,206/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$770万
+$27,116/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$772万
+$27,169/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$876万
+$26,963/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1085万
+$26,345/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$722万
+$25,087/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 287呎 (1房)
+$744万
+$25,920/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+$762万
+$26,820/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$763万
+$26,873/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$867万
+$26,668/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+$1074万
+$26,061/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$715万
+$24,812/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 247呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$753万
+$26,339/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$755万
+$26,581/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 325呎 (1房)
+$857万
+$26,375/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 374呎 (2房)
+$1350万
+$36,096/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>F | 251呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -763,6 +787,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -813,6 +857,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -863,6 +927,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -913,6 +997,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -963,6 +1067,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1013,6 +1137,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1063,6 +1207,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1113,6 +1277,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1163,6 +1347,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1213,6 +1417,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1263,6 +1487,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1313,6 +1557,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1359,6 +1623,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1405,6 +1689,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1451,6 +1755,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1497,6 +1821,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1543,6 +1887,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1589,6 +1953,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1635,6 +2019,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1681,6 +2085,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1727,6 +2151,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1773,6 +2217,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1819,6 +2283,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1869,6 +2353,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1919,6 +2423,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1969,6 +2493,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2019,6 +2563,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2069,6 +2633,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2119,6 +2703,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2165,6 +2769,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2211,6 +2835,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2257,6 +2901,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2303,6 +2967,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2349,6 +3033,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2395,6 +3099,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2441,6 +3165,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2487,6 +3231,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2533,6 +3297,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2579,6 +3363,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2625,6 +3429,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2671,6 +3495,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2717,6 +3561,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2763,6 +3627,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2809,6 +3693,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2855,6 +3759,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2901,6 +3825,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2947,6 +3891,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2993,6 +3957,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3039,6 +4023,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3085,6 +4089,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3131,6 +4155,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3177,6 +4221,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3223,6 +4287,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3269,6 +4353,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3315,6 +4419,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3361,6 +4485,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3407,6 +4551,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3453,6 +4617,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3499,6 +4683,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3545,6 +4749,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3591,6 +4815,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3637,6 +4881,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3683,6 +4947,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3729,6 +5013,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3775,6 +5079,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3821,6 +5145,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3867,6 +5211,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3913,6 +5277,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3959,6 +5343,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4005,6 +5409,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4051,6 +5475,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4097,6 +5541,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4143,6 +5607,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4189,6 +5673,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4235,6 +5739,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4281,6 +5805,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4327,6 +5871,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4373,6 +5937,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4419,6 +6003,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4465,6 +6069,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4511,6 +6135,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4557,6 +6201,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4603,6 +6267,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4649,6 +6333,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4695,6 +6399,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4741,6 +6465,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4787,6 +6531,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4833,6 +6597,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4879,6 +6663,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4925,6 +6729,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4971,6 +6795,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5017,6 +6861,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5063,6 +6927,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5109,6 +6993,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5155,6 +7059,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5201,6 +7125,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5247,6 +7191,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5293,6 +7257,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5339,6 +7323,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5385,6 +7389,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5431,6 +7455,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5477,6 +7521,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5523,6 +7587,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5569,6 +7653,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5615,6 +7719,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5661,6 +7785,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5707,6 +7851,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5753,6 +7917,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5799,6 +7983,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5845,6 +8049,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5891,6 +8115,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5937,6 +8181,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5983,6 +8247,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6029,6 +8313,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6075,6 +8379,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6121,6 +8445,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6167,6 +8511,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6213,6 +8577,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6259,6 +8643,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6309,6 +8713,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6355,6 +8779,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6401,6 +8845,26 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6447,6 +8911,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6493,6 +8977,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6543,13 +9047,33 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6809,7 +9333,7 @@
           <t>A | 287呎 (1房)
 $1016万
 $35,401/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -6817,7 +9341,7 @@
           <t>B | 284呎 (1房)
 $1026万
 $36,144/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -6825,7 +9349,7 @@
           <t>C | 284呎 (1房)
 $1028万
 $36,215/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -6833,7 +9357,7 @@
           <t>D | 325呎 (1房)
 $1153万
 $35,477/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -6841,7 +9365,7 @@
           <t>E | 412呎 (2房)
 $1425万
 $34,587/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -6864,7 +9388,7 @@
           <t>A | 287呎 (1房)
 $994万
 $34,627/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -6872,7 +9396,7 @@
           <t>B | 284呎 (1房)
 $1011万
 $35,595/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -6880,7 +9404,7 @@
           <t>C | 284呎 (1房)
 $1013万
 $35,665/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -6888,7 +9412,7 @@
           <t>D | 325呎 (1房)
 $1139万
 $35,040/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -6896,7 +9420,7 @@
           <t>E | 412呎 (2房)
 $1410万
 $34,223/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -6904,7 +9428,7 @@
           <t>F | 288呎 (1房)
 $993万
 $34,479/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -6974,7 +9498,7 @@
           <t>A | 287呎 (1房)
 $953万
 $33,206/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -6982,7 +9506,7 @@
           <t>B | 284呎 (1房)
 $977万
 $34,398/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -6990,7 +9514,7 @@
           <t>C | 284呎 (1房)
 $980万
 $34,507/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -6998,7 +9522,7 @@
           <t>D | 325呎 (1房)
 $1110万
 $34,154/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -7006,7 +9530,7 @@
           <t>E | 412呎 (2房)
 $1376万
 $33,400/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -7014,7 +9538,7 @@
           <t>F | 288呎 (1房)
 $915万
 $31,771/呎
-(26年-03月)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -7029,7 +9553,7 @@
           <t>A | 287呎 (1房)
 $924万
 $32,181/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -7037,7 +9561,7 @@
           <t>B | 284呎 (1房)
 $946万
 $33,327/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -7045,7 +9569,7 @@
           <t>C | 284呎 (1房)
 $948万
 $33,373/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -7053,7 +9577,7 @@
           <t>D | 325呎 (1房)
 $1076万
 $33,108/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -7061,7 +9585,7 @@
           <t>E | 412呎 (2房)
 $1333万
 $32,354/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -7069,7 +9593,7 @@
           <t>F | 288呎 (1房)
 $896万
 $31,111/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -7084,7 +9608,7 @@
           <t>A | 287呎 (1房)
 $916万
 $31,923/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -7092,7 +9616,7 @@
           <t>B | 284呎 (1房)
 $937万
 $33,000/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -7100,7 +9624,7 @@
           <t>C | 284呎 (1房)
 $940万
 $33,081/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -7108,7 +9632,7 @@
           <t>D | 325呎 (1房)
 $1078万
 $33,169/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -7116,7 +9640,7 @@
           <t>E | 412呎 (2房)
 $1322万
 $32,095/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -7124,7 +9648,7 @@
           <t>F | 288呎 (1房)
 $898万
 $31,181/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -7139,7 +9663,7 @@
           <t>A | 287呎 (1房)
 $903万
 $31,470/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7147,7 +9671,7 @@
           <t>B | 284呎 (1房)
 $927万
 $32,637/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -7155,7 +9679,7 @@
           <t>C | 284呎 (1房)
 $929万
 $32,701/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -7163,7 +9687,7 @@
           <t>D | 325呎 (1房)
 $1056万
 $32,477/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -7171,7 +9695,7 @@
           <t>E | 412呎 (2房)
 $1307万
 $31,728/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -7179,7 +9703,7 @@
           <t>F | 288呎 (1房)
 $868万
 $30,139/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -7194,7 +9718,7 @@
           <t>A | 287呎 (1房)
 $898万
 $31,300/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -7202,7 +9726,7 @@
           <t>B | 284呎 (1房)
 $918万
 $32,324/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -7210,7 +9734,7 @@
           <t>C | 284呎 (1房)
 $920万
 $32,377/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -7218,7 +9742,7 @@
           <t>D | 325呎 (1房)
 $1045万
 $32,154/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -7226,7 +9750,7 @@
           <t>E | 412呎 (2房)
 $1294万
 $31,415/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -7234,7 +9758,7 @@
           <t>F | 288呎 (1房)
 $860万
 $29,858/呎
-(26年-03月)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
     </row>
@@ -7249,7 +9773,7 @@
           <t>A | 287呎 (1房)
 $868万
 $30,244/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -7257,7 +9781,7 @@
           <t>B | 284呎 (1房)
 $888万
 $31,268/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -7265,7 +9789,7 @@
           <t>C | 284呎 (1房)
 $891万
 $31,359/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -7273,7 +9797,7 @@
           <t>D | 325呎 (1房)
 $1023万
 $31,477/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -7281,7 +9805,7 @@
           <t>E | 412呎 (2房)
 $1253万
 $30,408/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -7289,7 +9813,7 @@
           <t>F | 288呎 (1房)
 $834万
 $28,951/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -7304,7 +9828,7 @@
           <t>A | 287呎 (1房)
 $812万
 $28,310/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7312,7 +9836,7 @@
           <t>B | 284呎 (1房)
 $832万
 $29,296/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -7320,7 +9844,7 @@
           <t>C | 284呎 (1房)
 $834万
 $29,352/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -7328,7 +9852,7 @@
           <t>D | 325呎 (1房)
 $947万
 $29,129/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -7336,7 +9860,7 @@
           <t>E | 412呎 (2房)
 $1173万
 $28,464/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -7344,7 +9868,7 @@
           <t>F | 288呎 (1房)
 $780万
 $27,101/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -7359,7 +9883,7 @@
           <t>A | 287呎 (1房)
 $804万
 $28,000/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7367,7 +9891,7 @@
           <t>B | 284呎 (1房)
 $823万
 $28,972/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7375,7 +9899,7 @@
           <t>C | 284呎 (1房)
 $824万
 $29,028/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -7383,7 +9907,7 @@
           <t>D | 325呎 (1房)
 $936万
 $28,806/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -7391,7 +9915,7 @@
           <t>E | 412呎 (2房)
 $1160万
 $28,148/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -7399,7 +9923,7 @@
           <t>F | 288呎 (1房)
 $772万
 $26,802/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -7414,7 +9938,7 @@
           <t>A | 287呎 (1房)
 $821万
 $28,596/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7422,7 +9946,7 @@
           <t>B | 284呎 (1房)
 $843万
 $29,683/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7430,7 +9954,7 @@
           <t>C | 284呎 (1房)
 $845万
 $29,754/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -7438,7 +9962,7 @@
           <t>D | 325呎 (1房)
 $956万
 $29,422/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -7446,7 +9970,7 @@
           <t>E | 412呎 (2房)
 $1184万
 $28,750/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -7454,7 +9978,7 @@
           <t>F | 288呎 (1房)
 $788万
 $27,375/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -7469,7 +9993,7 @@
           <t>A | 287呎 (1房)
 $786万
 $27,401/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -7477,7 +10001,7 @@
           <t>B | 284呎 (1房)
 $805万
 $28,352/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -7485,7 +10009,7 @@
           <t>C | 284呎 (1房)
 $807万
 $28,408/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -7493,7 +10017,7 @@
           <t>D | 325呎 (1房)
 $916万
 $28,191/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -7501,7 +10025,7 @@
           <t>E | 412呎 (2房)
 $1135万
 $27,546/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -7509,7 +10033,7 @@
           <t>F | 288呎 (1房)
 $755万
 $26,229/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -7524,7 +10048,7 @@
           <t>A | 287呎 (1房)
 $778万
 $27,115/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7532,7 +10056,7 @@
           <t>B | 284呎 (1房)
 $797万
 $28,060/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7540,7 +10064,7 @@
           <t>C | 284呎 (1房)
 $798万
 $28,113/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -7548,7 +10072,7 @@
           <t>D | 325呎 (1房)
 $907万
 $27,898/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -7556,7 +10080,7 @@
           <t>E | 412呎 (2房)
 $1123万
 $27,262/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -7564,7 +10088,7 @@
           <t>F | 288呎 (1房)
 $748万
 $25,958/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -7579,7 +10103,7 @@
           <t>A | 287呎 (1房)
 $769万
 $26,805/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -7587,7 +10111,7 @@
           <t>B | 284呎 (1房)
 $788万
 $27,732/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -7595,7 +10119,7 @@
           <t>C | 284呎 (1房)
 $789万
 $27,792/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -7603,7 +10127,7 @@
           <t>D | 325呎 (1房)
 $896万
 $27,578/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -7611,7 +10135,7 @@
           <t>E | 412呎 (2房)
 $1110万
 $26,947/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -7619,7 +10143,7 @@
           <t>F | 288呎 (1房)
 $739万
 $25,656/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -7634,7 +10158,7 @@
           <t>A | 287呎 (1房)
 $761万
 $26,519/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -7642,7 +10166,7 @@
           <t>B | 284呎 (1房)
 $779万
 $27,440/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -7650,7 +10174,7 @@
           <t>C | 284呎 (1房)
 $781万
 $27,496/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -7658,7 +10182,7 @@
           <t>D | 325呎 (1房)
 $887万
 $27,283/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -7666,7 +10190,7 @@
           <t>E | 412呎 (2房)
 $1098万
 $26,660/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -7674,7 +10198,7 @@
           <t>F | 288呎 (1房)
 $731万
 $25,385/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -7689,7 +10213,7 @@
           <t>A | 287呎 (1房)
 $752万
 $26,206/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -7697,7 +10221,7 @@
           <t>B | 284呎 (1房)
 $770万
 $27,116/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -7705,7 +10229,7 @@
           <t>C | 284呎 (1房)
 $772万
 $27,169/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -7713,7 +10237,7 @@
           <t>D | 325呎 (1房)
 $876万
 $26,963/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -7721,7 +10245,7 @@
           <t>E | 412呎 (2房)
 $1085万
 $26,345/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -7729,7 +10253,7 @@
           <t>F | 288呎 (1房)
 $722万
 $25,087/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -7744,7 +10268,7 @@
           <t>A | 287呎 (1房)
 $744万
 $25,920/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -7752,7 +10276,7 @@
           <t>B | 284呎 (1房)
 $762万
 $26,820/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -7760,7 +10284,7 @@
           <t>C | 284呎 (1房)
 $763万
 $26,873/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -7768,7 +10292,7 @@
           <t>D | 325呎 (1房)
 $867万
 $26,668/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -7776,7 +10300,7 @@
           <t>E | 412呎 (2房)
 $1074万
 $26,061/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -7784,7 +10308,7 @@
           <t>F | 288呎 (1房)
 $715万
 $24,812/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -7807,7 +10331,7 @@
           <t>B | 286呎 (1房)
 $753万
 $26,339/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -7815,7 +10339,7 @@
           <t>C | 284呎 (1房)
 $755万
 $26,581/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -7823,7 +10347,7 @@
           <t>D | 325呎 (1房)
 $857万
 $26,375/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -7831,7 +10355,7 @@
           <t>E | 374呎 (2房)
 $1350万
 $36,096/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">

--- a/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -9333,7 +9333,7 @@
           <t>A | 287呎 (1房)
 $1016万
 $35,401/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -9341,7 +9341,7 @@
           <t>B | 284呎 (1房)
 $1026万
 $36,144/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -9349,7 +9349,7 @@
           <t>C | 284呎 (1房)
 $1028万
 $36,215/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -9357,7 +9357,7 @@
           <t>D | 325呎 (1房)
 $1153万
 $35,477/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -9365,7 +9365,7 @@
           <t>E | 412呎 (2房)
 $1425万
 $34,587/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -9388,7 +9388,7 @@
           <t>A | 287呎 (1房)
 $994万
 $34,627/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -9396,7 +9396,7 @@
           <t>B | 284呎 (1房)
 $1011万
 $35,595/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -9404,7 +9404,7 @@
           <t>C | 284呎 (1房)
 $1013万
 $35,665/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -9412,7 +9412,7 @@
           <t>D | 325呎 (1房)
 $1139万
 $35,040/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -9420,7 +9420,7 @@
           <t>E | 412呎 (2房)
 $1410万
 $34,223/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -9428,7 +9428,7 @@
           <t>F | 288呎 (1房)
 $993万
 $34,479/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
           <t>A | 287呎 (1房)
 $953万
 $33,206/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -9506,7 +9506,7 @@
           <t>B | 284呎 (1房)
 $977万
 $34,398/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -9514,7 +9514,7 @@
           <t>C | 284呎 (1房)
 $980万
 $34,507/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -9522,7 +9522,7 @@
           <t>D | 325呎 (1房)
 $1110万
 $34,154/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -9530,7 +9530,7 @@
           <t>E | 412呎 (2房)
 $1376万
 $33,400/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -9538,7 +9538,7 @@
           <t>F | 288呎 (1房)
 $915万
 $31,771/呎
-(26年-03月-20日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
           <t>A | 287呎 (1房)
 $924万
 $32,181/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -9561,7 +9561,7 @@
           <t>B | 284呎 (1房)
 $946万
 $33,327/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -9569,7 +9569,7 @@
           <t>C | 284呎 (1房)
 $948万
 $33,373/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -9577,7 +9577,7 @@
           <t>D | 325呎 (1房)
 $1076万
 $33,108/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -9585,7 +9585,7 @@
           <t>E | 412呎 (2房)
 $1333万
 $32,354/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -9593,7 +9593,7 @@
           <t>F | 288呎 (1房)
 $896万
 $31,111/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
           <t>A | 287呎 (1房)
 $916万
 $31,923/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -9616,7 +9616,7 @@
           <t>B | 284呎 (1房)
 $937万
 $33,000/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -9624,7 +9624,7 @@
           <t>C | 284呎 (1房)
 $940万
 $33,081/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -9632,7 +9632,7 @@
           <t>D | 325呎 (1房)
 $1078万
 $33,169/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -9640,7 +9640,7 @@
           <t>E | 412呎 (2房)
 $1322万
 $32,095/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -9648,7 +9648,7 @@
           <t>F | 288呎 (1房)
 $898万
 $31,181/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9663,7 @@
           <t>A | 287呎 (1房)
 $903万
 $31,470/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -9671,7 +9671,7 @@
           <t>B | 284呎 (1房)
 $927万
 $32,637/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -9679,7 +9679,7 @@
           <t>C | 284呎 (1房)
 $929万
 $32,701/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -9687,7 +9687,7 @@
           <t>D | 325呎 (1房)
 $1056万
 $32,477/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -9695,7 +9695,7 @@
           <t>E | 412呎 (2房)
 $1307万
 $31,728/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -9703,7 +9703,7 @@
           <t>F | 288呎 (1房)
 $868万
 $30,139/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
           <t>A | 287呎 (1房)
 $898万
 $31,300/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -9726,7 +9726,7 @@
           <t>B | 284呎 (1房)
 $918万
 $32,324/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -9734,7 +9734,7 @@
           <t>C | 284呎 (1房)
 $920万
 $32,377/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -9742,7 +9742,7 @@
           <t>D | 325呎 (1房)
 $1045万
 $32,154/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -9750,7 +9750,7 @@
           <t>E | 412呎 (2房)
 $1294万
 $31,415/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -9758,7 +9758,7 @@
           <t>F | 288呎 (1房)
 $860万
 $29,858/呎
-(26年-03月-13日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
           <t>A | 287呎 (1房)
 $868万
 $30,244/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -9781,7 +9781,7 @@
           <t>B | 284呎 (1房)
 $888万
 $31,268/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -9789,7 +9789,7 @@
           <t>C | 284呎 (1房)
 $891万
 $31,359/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -9797,7 +9797,7 @@
           <t>D | 325呎 (1房)
 $1023万
 $31,477/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -9805,7 +9805,7 @@
           <t>E | 412呎 (2房)
 $1253万
 $30,408/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -9813,7 +9813,7 @@
           <t>F | 288呎 (1房)
 $834万
 $28,951/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
           <t>A | 287呎 (1房)
 $812万
 $28,310/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -9836,7 +9836,7 @@
           <t>B | 284呎 (1房)
 $832万
 $29,296/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -9844,7 +9844,7 @@
           <t>C | 284呎 (1房)
 $834万
 $29,352/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -9852,7 +9852,7 @@
           <t>D | 325呎 (1房)
 $947万
 $29,129/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -9860,7 +9860,7 @@
           <t>E | 412呎 (2房)
 $1173万
 $28,464/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -9868,7 +9868,7 @@
           <t>F | 288呎 (1房)
 $780万
 $27,101/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
           <t>A | 287呎 (1房)
 $804万
 $28,000/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -9891,7 +9891,7 @@
           <t>B | 284呎 (1房)
 $823万
 $28,972/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -9899,7 +9899,7 @@
           <t>C | 284呎 (1房)
 $824万
 $29,028/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -9907,7 +9907,7 @@
           <t>D | 325呎 (1房)
 $936万
 $28,806/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -9915,7 +9915,7 @@
           <t>E | 412呎 (2房)
 $1160万
 $28,148/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -9923,7 +9923,7 @@
           <t>F | 288呎 (1房)
 $772万
 $26,802/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
           <t>A | 287呎 (1房)
 $821万
 $28,596/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -9946,7 +9946,7 @@
           <t>B | 284呎 (1房)
 $843万
 $29,683/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -9954,7 +9954,7 @@
           <t>C | 284呎 (1房)
 $845万
 $29,754/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -9962,7 +9962,7 @@
           <t>D | 325呎 (1房)
 $956万
 $29,422/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -9970,7 +9970,7 @@
           <t>E | 412呎 (2房)
 $1184万
 $28,750/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -9978,7 +9978,7 @@
           <t>F | 288呎 (1房)
 $788万
 $27,375/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
           <t>A | 287呎 (1房)
 $786万
 $27,401/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -10001,7 +10001,7 @@
           <t>B | 284呎 (1房)
 $805万
 $28,352/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -10009,7 +10009,7 @@
           <t>C | 284呎 (1房)
 $807万
 $28,408/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -10017,7 +10017,7 @@
           <t>D | 325呎 (1房)
 $916万
 $28,191/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -10025,7 +10025,7 @@
           <t>E | 412呎 (2房)
 $1135万
 $27,546/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -10033,7 +10033,7 @@
           <t>F | 288呎 (1房)
 $755万
 $26,229/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
           <t>A | 287呎 (1房)
 $778万
 $27,115/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -10056,7 +10056,7 @@
           <t>B | 284呎 (1房)
 $797万
 $28,060/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -10064,7 +10064,7 @@
           <t>C | 284呎 (1房)
 $798万
 $28,113/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -10072,7 +10072,7 @@
           <t>D | 325呎 (1房)
 $907万
 $27,898/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -10080,7 +10080,7 @@
           <t>E | 412呎 (2房)
 $1123万
 $27,262/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -10088,7 +10088,7 @@
           <t>F | 288呎 (1房)
 $748万
 $25,958/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
           <t>A | 287呎 (1房)
 $769万
 $26,805/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -10111,7 +10111,7 @@
           <t>B | 284呎 (1房)
 $788万
 $27,732/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -10119,7 +10119,7 @@
           <t>C | 284呎 (1房)
 $789万
 $27,792/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -10127,7 +10127,7 @@
           <t>D | 325呎 (1房)
 $896万
 $27,578/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -10135,7 +10135,7 @@
           <t>E | 412呎 (2房)
 $1110万
 $26,947/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -10143,7 +10143,7 @@
           <t>F | 288呎 (1房)
 $739万
 $25,656/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
           <t>A | 287呎 (1房)
 $761万
 $26,519/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -10166,7 +10166,7 @@
           <t>B | 284呎 (1房)
 $779万
 $27,440/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -10174,7 +10174,7 @@
           <t>C | 284呎 (1房)
 $781万
 $27,496/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -10182,7 +10182,7 @@
           <t>D | 325呎 (1房)
 $887万
 $27,283/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -10190,7 +10190,7 @@
           <t>E | 412呎 (2房)
 $1098万
 $26,660/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -10198,7 +10198,7 @@
           <t>F | 288呎 (1房)
 $731万
 $25,385/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10213,7 @@
           <t>A | 287呎 (1房)
 $752万
 $26,206/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -10221,7 +10221,7 @@
           <t>B | 284呎 (1房)
 $770万
 $27,116/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -10229,7 +10229,7 @@
           <t>C | 284呎 (1房)
 $772万
 $27,169/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -10237,7 +10237,7 @@
           <t>D | 325呎 (1房)
 $876万
 $26,963/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -10245,7 +10245,7 @@
           <t>E | 412呎 (2房)
 $1085万
 $26,345/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -10253,7 +10253,7 @@
           <t>F | 288呎 (1房)
 $722万
 $25,087/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
           <t>A | 287呎 (1房)
 $744万
 $25,920/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -10276,7 +10276,7 @@
           <t>B | 284呎 (1房)
 $762万
 $26,820/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -10284,7 +10284,7 @@
           <t>C | 284呎 (1房)
 $763万
 $26,873/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -10292,7 +10292,7 @@
           <t>D | 325呎 (1房)
 $867万
 $26,668/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -10300,7 +10300,7 @@
           <t>E | 412呎 (2房)
 $1074万
 $26,061/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -10308,7 +10308,7 @@
           <t>F | 288呎 (1房)
 $715万
 $24,812/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
           <t>B | 286呎 (1房)
 $753万
 $26,339/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -10339,7 +10339,7 @@
           <t>C | 284呎 (1房)
 $755万
 $26,581/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -10347,7 +10347,7 @@
           <t>D | 325呎 (1房)
 $857万
 $26,375/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -10355,7 +10355,7 @@
           <t>E | 374呎 (2房)
 $1350万
 $36,096/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">

--- a/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -9333,7 +9333,7 @@
           <t>A | 287呎 (1房)
 $1016万
 $35,401/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -9341,7 +9341,7 @@
           <t>B | 284呎 (1房)
 $1026万
 $36,144/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -9349,7 +9349,7 @@
           <t>C | 284呎 (1房)
 $1028万
 $36,215/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -9357,7 +9357,7 @@
           <t>D | 325呎 (1房)
 $1153万
 $35,477/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -9365,7 +9365,7 @@
           <t>E | 412呎 (2房)
 $1425万
 $34,587/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -9388,7 +9388,7 @@
           <t>A | 287呎 (1房)
 $994万
 $34,627/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -9396,7 +9396,7 @@
           <t>B | 284呎 (1房)
 $1011万
 $35,595/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -9404,7 +9404,7 @@
           <t>C | 284呎 (1房)
 $1013万
 $35,665/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -9412,7 +9412,7 @@
           <t>D | 325呎 (1房)
 $1139万
 $35,040/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -9420,7 +9420,7 @@
           <t>E | 412呎 (2房)
 $1410万
 $34,223/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -9428,7 +9428,7 @@
           <t>F | 288呎 (1房)
 $993万
 $34,479/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
           <t>A | 287呎 (1房)
 $953万
 $33,206/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -9506,7 +9506,7 @@
           <t>B | 284呎 (1房)
 $977万
 $34,398/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -9514,7 +9514,7 @@
           <t>C | 284呎 (1房)
 $980万
 $34,507/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -9522,7 +9522,7 @@
           <t>D | 325呎 (1房)
 $1110万
 $34,154/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -9530,7 +9530,7 @@
           <t>E | 412呎 (2房)
 $1376万
 $33,400/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -9538,7 +9538,7 @@
           <t>F | 288呎 (1房)
 $915万
 $31,771/呎
-(26年-03月)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
           <t>A | 287呎 (1房)
 $924万
 $32,181/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -9561,7 +9561,7 @@
           <t>B | 284呎 (1房)
 $946万
 $33,327/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -9569,7 +9569,7 @@
           <t>C | 284呎 (1房)
 $948万
 $33,373/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -9577,7 +9577,7 @@
           <t>D | 325呎 (1房)
 $1076万
 $33,108/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -9585,7 +9585,7 @@
           <t>E | 412呎 (2房)
 $1333万
 $32,354/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -9593,7 +9593,7 @@
           <t>F | 288呎 (1房)
 $896万
 $31,111/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
           <t>A | 287呎 (1房)
 $916万
 $31,923/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -9616,7 +9616,7 @@
           <t>B | 284呎 (1房)
 $937万
 $33,000/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -9624,7 +9624,7 @@
           <t>C | 284呎 (1房)
 $940万
 $33,081/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -9632,7 +9632,7 @@
           <t>D | 325呎 (1房)
 $1078万
 $33,169/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -9640,7 +9640,7 @@
           <t>E | 412呎 (2房)
 $1322万
 $32,095/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -9648,7 +9648,7 @@
           <t>F | 288呎 (1房)
 $898万
 $31,181/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9663,7 @@
           <t>A | 287呎 (1房)
 $903万
 $31,470/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -9671,7 +9671,7 @@
           <t>B | 284呎 (1房)
 $927万
 $32,637/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -9679,7 +9679,7 @@
           <t>C | 284呎 (1房)
 $929万
 $32,701/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -9687,7 +9687,7 @@
           <t>D | 325呎 (1房)
 $1056万
 $32,477/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -9695,7 +9695,7 @@
           <t>E | 412呎 (2房)
 $1307万
 $31,728/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -9703,7 +9703,7 @@
           <t>F | 288呎 (1房)
 $868万
 $30,139/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
           <t>A | 287呎 (1房)
 $898万
 $31,300/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -9726,7 +9726,7 @@
           <t>B | 284呎 (1房)
 $918万
 $32,324/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -9734,7 +9734,7 @@
           <t>C | 284呎 (1房)
 $920万
 $32,377/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -9742,7 +9742,7 @@
           <t>D | 325呎 (1房)
 $1045万
 $32,154/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -9750,7 +9750,7 @@
           <t>E | 412呎 (2房)
 $1294万
 $31,415/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -9758,7 +9758,7 @@
           <t>F | 288呎 (1房)
 $860万
 $29,858/呎
-(26年-03月)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
           <t>A | 287呎 (1房)
 $868万
 $30,244/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -9781,7 +9781,7 @@
           <t>B | 284呎 (1房)
 $888万
 $31,268/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -9789,7 +9789,7 @@
           <t>C | 284呎 (1房)
 $891万
 $31,359/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -9797,7 +9797,7 @@
           <t>D | 325呎 (1房)
 $1023万
 $31,477/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -9805,7 +9805,7 @@
           <t>E | 412呎 (2房)
 $1253万
 $30,408/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -9813,7 +9813,7 @@
           <t>F | 288呎 (1房)
 $834万
 $28,951/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
           <t>A | 287呎 (1房)
 $812万
 $28,310/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -9836,7 +9836,7 @@
           <t>B | 284呎 (1房)
 $832万
 $29,296/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -9844,7 +9844,7 @@
           <t>C | 284呎 (1房)
 $834万
 $29,352/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -9852,7 +9852,7 @@
           <t>D | 325呎 (1房)
 $947万
 $29,129/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -9860,7 +9860,7 @@
           <t>E | 412呎 (2房)
 $1173万
 $28,464/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -9868,7 +9868,7 @@
           <t>F | 288呎 (1房)
 $780万
 $27,101/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
           <t>A | 287呎 (1房)
 $804万
 $28,000/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -9891,7 +9891,7 @@
           <t>B | 284呎 (1房)
 $823万
 $28,972/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -9899,7 +9899,7 @@
           <t>C | 284呎 (1房)
 $824万
 $29,028/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -9907,7 +9907,7 @@
           <t>D | 325呎 (1房)
 $936万
 $28,806/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -9915,7 +9915,7 @@
           <t>E | 412呎 (2房)
 $1160万
 $28,148/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -9923,7 +9923,7 @@
           <t>F | 288呎 (1房)
 $772万
 $26,802/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
           <t>A | 287呎 (1房)
 $821万
 $28,596/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -9946,7 +9946,7 @@
           <t>B | 284呎 (1房)
 $843万
 $29,683/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -9954,7 +9954,7 @@
           <t>C | 284呎 (1房)
 $845万
 $29,754/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -9962,7 +9962,7 @@
           <t>D | 325呎 (1房)
 $956万
 $29,422/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -9970,7 +9970,7 @@
           <t>E | 412呎 (2房)
 $1184万
 $28,750/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -9978,7 +9978,7 @@
           <t>F | 288呎 (1房)
 $788万
 $27,375/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
           <t>A | 287呎 (1房)
 $786万
 $27,401/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -10001,7 +10001,7 @@
           <t>B | 284呎 (1房)
 $805万
 $28,352/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -10009,7 +10009,7 @@
           <t>C | 284呎 (1房)
 $807万
 $28,408/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -10017,7 +10017,7 @@
           <t>D | 325呎 (1房)
 $916万
 $28,191/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -10025,7 +10025,7 @@
           <t>E | 412呎 (2房)
 $1135万
 $27,546/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -10033,7 +10033,7 @@
           <t>F | 288呎 (1房)
 $755万
 $26,229/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
           <t>A | 287呎 (1房)
 $778万
 $27,115/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -10056,7 +10056,7 @@
           <t>B | 284呎 (1房)
 $797万
 $28,060/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -10064,7 +10064,7 @@
           <t>C | 284呎 (1房)
 $798万
 $28,113/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -10072,7 +10072,7 @@
           <t>D | 325呎 (1房)
 $907万
 $27,898/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -10080,7 +10080,7 @@
           <t>E | 412呎 (2房)
 $1123万
 $27,262/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -10088,7 +10088,7 @@
           <t>F | 288呎 (1房)
 $748万
 $25,958/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
           <t>A | 287呎 (1房)
 $769万
 $26,805/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -10111,7 +10111,7 @@
           <t>B | 284呎 (1房)
 $788万
 $27,732/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -10119,7 +10119,7 @@
           <t>C | 284呎 (1房)
 $789万
 $27,792/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -10127,7 +10127,7 @@
           <t>D | 325呎 (1房)
 $896万
 $27,578/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -10135,7 +10135,7 @@
           <t>E | 412呎 (2房)
 $1110万
 $26,947/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -10143,7 +10143,7 @@
           <t>F | 288呎 (1房)
 $739万
 $25,656/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
           <t>A | 287呎 (1房)
 $761万
 $26,519/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -10166,7 +10166,7 @@
           <t>B | 284呎 (1房)
 $779万
 $27,440/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -10174,7 +10174,7 @@
           <t>C | 284呎 (1房)
 $781万
 $27,496/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -10182,7 +10182,7 @@
           <t>D | 325呎 (1房)
 $887万
 $27,283/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -10190,7 +10190,7 @@
           <t>E | 412呎 (2房)
 $1098万
 $26,660/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -10198,7 +10198,7 @@
           <t>F | 288呎 (1房)
 $731万
 $25,385/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10213,7 @@
           <t>A | 287呎 (1房)
 $752万
 $26,206/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -10221,7 +10221,7 @@
           <t>B | 284呎 (1房)
 $770万
 $27,116/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -10229,7 +10229,7 @@
           <t>C | 284呎 (1房)
 $772万
 $27,169/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -10237,7 +10237,7 @@
           <t>D | 325呎 (1房)
 $876万
 $26,963/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -10245,7 +10245,7 @@
           <t>E | 412呎 (2房)
 $1085万
 $26,345/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -10253,7 +10253,7 @@
           <t>F | 288呎 (1房)
 $722万
 $25,087/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
           <t>A | 287呎 (1房)
 $744万
 $25,920/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -10276,7 +10276,7 @@
           <t>B | 284呎 (1房)
 $762万
 $26,820/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -10284,7 +10284,7 @@
           <t>C | 284呎 (1房)
 $763万
 $26,873/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -10292,7 +10292,7 @@
           <t>D | 325呎 (1房)
 $867万
 $26,668/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -10300,7 +10300,7 @@
           <t>E | 412呎 (2房)
 $1074万
 $26,061/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -10308,7 +10308,7 @@
           <t>F | 288呎 (1房)
 $715万
 $24,812/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
           <t>B | 286呎 (1房)
 $753万
 $26,339/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -10339,7 +10339,7 @@
           <t>C | 284呎 (1房)
 $755万
 $26,581/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -10347,7 +10347,7 @@
           <t>D | 325呎 (1房)
 $857万
 $26,375/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -10355,7 +10355,7 @@
           <t>E | 374呎 (2房)
 $1350万
 $36,096/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
